--- a/data/trans_camb/IP15-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP15-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,95; 10,61</t>
+          <t>-8,62; 11,97</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,97; 15,78</t>
+          <t>-8,19; 14,96</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-9,4; 32,61</t>
+          <t>-9,31; 29,44</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-11,7; 9,4</t>
+          <t>-13,42; 7,92</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-20,62; -0,2</t>
+          <t>-20,13; -0,8</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-10,65; 13,86</t>
+          <t>-9,46; 14,45</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-8,31; 6,76</t>
+          <t>-8,46; 6,56</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-12,62; 3,61</t>
+          <t>-12,03; 3,53</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-5,85; 18,08</t>
+          <t>-6,22; 16,43</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-31,46; 57,54</t>
+          <t>-31,49; 67,35</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-31,78; 81,16</t>
+          <t>-30,36; 79,4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-36,49; 154,25</t>
+          <t>-38,06; 147,64</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-43,32; 56,19</t>
+          <t>-45,89; 44,38</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-73,26; 4,94</t>
+          <t>-71,92; -2,7</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-37,1; 79,45</t>
+          <t>-33,78; 78,78</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-29,7; 33,6</t>
+          <t>-30,75; 32,51</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-46,1; 17,5</t>
+          <t>-44,83; 16,61</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-22,83; 89,0</t>
+          <t>-25,03; 75,21</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,13; 4,66</t>
+          <t>-4,26; 4,29</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,37; 2,39</t>
+          <t>-6,04; 2,2</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,58; 21,57</t>
+          <t>0,67; 20,33</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 5,95</t>
+          <t>-1,96; 6,32</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,8; 2,77</t>
+          <t>-4,62; 3,35</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,29; 9,44</t>
+          <t>0,24; 9,39</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 3,96</t>
+          <t>-1,86; 4,26</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 1,33</t>
+          <t>-4,2; 1,34</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,84; 12,78</t>
+          <t>1,96; 12,93</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-19,09; 27,69</t>
+          <t>-19,92; 25,08</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-29,44; 14,55</t>
+          <t>-28,12; 12,74</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,39; 126,3</t>
+          <t>2,71; 120,95</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-13,01; 35,91</t>
+          <t>-9,6; 38,49</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-24,27; 16,87</t>
+          <t>-23,48; 21,26</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,96; 56,35</t>
+          <t>1,23; 56,2</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-9,36; 22,51</t>
+          <t>-8,87; 24,21</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-20,36; 7,59</t>
+          <t>-20,52; 7,9</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9,09; 70,58</t>
+          <t>9,03; 71,13</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,31; 15,98</t>
+          <t>2,42; 15,76</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 10,04</t>
+          <t>-2,55; 9,95</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,21; 22,04</t>
+          <t>6,76; 22,05</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,22; 8,54</t>
+          <t>-6,86; 8,1</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-13,86; -0,22</t>
+          <t>-13,67; 0,32</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 11,66</t>
+          <t>-4,66; 11,17</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,03; 10,15</t>
+          <t>0,31; 10,25</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-5,9; 3,39</t>
+          <t>-6,68; 2,91</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,38; 14,87</t>
+          <t>3,17; 14,53</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11,71; 158,62</t>
+          <t>12,29; 149,14</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-13,91; 100,65</t>
+          <t>-17,95; 92,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>40,01; 216,04</t>
+          <t>41,8; 220,56</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-24,89; 47,37</t>
+          <t>-26,82; 43,24</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-53,07; -2,47</t>
+          <t>-52,67; 2,05</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-17,62; 63,86</t>
+          <t>-18,74; 64,61</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,06; 65,52</t>
+          <t>0,97; 68,73</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-30,3; 23,35</t>
+          <t>-33,14; 18,7</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>22,35; 101,12</t>
+          <t>15,54; 97,79</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 6,0</t>
+          <t>-1,19; 5,73</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,84; 2,73</t>
+          <t>-3,52; 2,82</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,8; 18,59</t>
+          <t>3,58; 19,76</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 4,94</t>
+          <t>-2,07; 4,54</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-6,67; -0,34</t>
+          <t>-6,7; -0,13</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,19; 7,56</t>
+          <t>0,42; 7,99</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 4,09</t>
+          <t>-0,58; 4,32</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-4,32; 0,56</t>
+          <t>-4,23; 0,59</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,99; 11,21</t>
+          <t>3,12; 11,4</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 35,93</t>
+          <t>-6,23; 33,43</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-19,16; 16,14</t>
+          <t>-18,08; 16,95</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>19,35; 107,58</t>
+          <t>17,06; 110,18</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-10,34; 27,12</t>
+          <t>-9,93; 24,97</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-31,11; -1,78</t>
+          <t>-31,28; -0,1</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,89; 41,49</t>
+          <t>1,29; 43,97</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-3,33; 22,65</t>
+          <t>-2,85; 24,25</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-21,61; 2,97</t>
+          <t>-20,65; 3,12</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>15,0; 60,23</t>
+          <t>15,44; 63,78</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP15-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP15-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,62; 11,97</t>
+          <t>-10,01; 11,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,19; 14,96</t>
+          <t>-9,81; 13,17</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-9,31; 29,44</t>
+          <t>-8,43; 32,09</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-13,42; 7,92</t>
+          <t>-12,52; 8,01</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-20,13; -0,8</t>
+          <t>-20,55; -0,27</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-9,46; 14,45</t>
+          <t>-10,23; 13,74</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-8,46; 6,56</t>
+          <t>-8,11; 6,87</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-12,03; 3,53</t>
+          <t>-12,6; 3,38</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-6,22; 16,43</t>
+          <t>-6,34; 18,52</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-31,49; 67,35</t>
+          <t>-34,28; 59,63</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-30,36; 79,4</t>
+          <t>-34,57; 69,9</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-38,06; 147,64</t>
+          <t>-34,59; 156,69</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-45,89; 44,38</t>
+          <t>-43,97; 46,34</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-71,92; -2,7</t>
+          <t>-72,94; -0,14</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-33,78; 78,78</t>
+          <t>-39,63; 74,85</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-30,75; 32,51</t>
+          <t>-30,55; 34,28</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-44,83; 16,61</t>
+          <t>-44,6; 17,8</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-25,03; 75,21</t>
+          <t>-23,76; 95,7</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,26; 4,29</t>
+          <t>-4,22; 4,16</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,04; 2,2</t>
+          <t>-5,88; 2,27</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,67; 20,33</t>
+          <t>0,64; 22,02</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 6,32</t>
+          <t>-1,82; 6,53</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,62; 3,35</t>
+          <t>-5,09; 3,26</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,24; 9,39</t>
+          <t>0,61; 9,8</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 4,26</t>
+          <t>-1,71; 4,01</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,2; 1,34</t>
+          <t>-4,05; 1,87</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,96; 12,93</t>
+          <t>2,21; 13,24</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-19,92; 25,08</t>
+          <t>-19,88; 23,88</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-28,12; 12,74</t>
+          <t>-26,69; 13,33</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,71; 120,95</t>
+          <t>2,16; 122,39</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-9,6; 38,49</t>
+          <t>-9,44; 39,38</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-23,48; 21,26</t>
+          <t>-25,31; 20,64</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,23; 56,2</t>
+          <t>2,95; 58,72</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-8,87; 24,21</t>
+          <t>-8,33; 22,58</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-20,52; 7,9</t>
+          <t>-20,13; 10,71</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9,03; 71,13</t>
+          <t>10,44; 73,13</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,42; 15,76</t>
+          <t>2,61; 15,72</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 9,95</t>
+          <t>-2,25; 10,09</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,76; 22,05</t>
+          <t>7,79; 22,24</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,86; 8,1</t>
+          <t>-6,73; 8,04</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-13,67; 0,32</t>
+          <t>-13,54; -0,16</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,66; 11,17</t>
+          <t>-4,75; 10,76</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,31; 10,25</t>
+          <t>-0,44; 9,87</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-6,68; 2,91</t>
+          <t>-6,15; 3,07</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,17; 14,53</t>
+          <t>3,62; 14,33</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>12,29; 149,14</t>
+          <t>16,63; 161,66</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-17,95; 92,0</t>
+          <t>-14,33; 102,46</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>41,8; 220,56</t>
+          <t>48,77; 215,34</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-26,82; 43,24</t>
+          <t>-26,32; 44,24</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-52,67; 2,05</t>
+          <t>-53,51; -0,88</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-18,74; 64,61</t>
+          <t>-17,89; 57,67</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,97; 68,73</t>
+          <t>-2,49; 65,73</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-33,14; 18,7</t>
+          <t>-30,87; 19,94</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>15,54; 97,79</t>
+          <t>17,75; 96,07</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 5,73</t>
+          <t>-1,29; 5,9</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 2,82</t>
+          <t>-3,86; 2,64</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,58; 19,76</t>
+          <t>3,12; 18,36</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 4,54</t>
+          <t>-2,14; 4,62</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-6,7; -0,13</t>
+          <t>-6,51; 0,2</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,42; 7,99</t>
+          <t>0,72; 8,28</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 4,32</t>
+          <t>-0,75; 4,21</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-4,23; 0,59</t>
+          <t>-4,05; 0,71</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,12; 11,4</t>
+          <t>3,18; 10,76</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-6,23; 33,43</t>
+          <t>-6,72; 34,41</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-18,08; 16,95</t>
+          <t>-19,63; 15,96</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>17,06; 110,18</t>
+          <t>15,08; 101,97</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-9,93; 24,97</t>
+          <t>-10,21; 25,26</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-31,28; -0,1</t>
+          <t>-30,17; 1,54</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,29; 43,97</t>
+          <t>3,21; 46,1</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 24,25</t>
+          <t>-3,78; 23,94</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-20,65; 3,12</t>
+          <t>-20,01; 3,96</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>15,44; 63,78</t>
+          <t>15,24; 58,33</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP15-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP15-Estudios-trans_camb.xlsx
@@ -523,20 +523,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos (gotas/pastillas, inyecciones, supositorios,etc..)</t>
+          <t>Menores que consumieron algún tipo de medicamento en las últimas 2 semanas</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-2,32</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-10,52</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1,21</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>0,7</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>2,16</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>5,49</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-2,32</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-10,52</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,94</t>
+          <t>-2,95</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3,49</t>
+          <t>-0,71</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-10,01; 11,04</t>
+          <t>-11,7; 9,4</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,81; 13,17</t>
+          <t>-20,62; -0,2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-8,43; 32,09</t>
+          <t>-10,35; 14,25</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-12,52; 8,01</t>
+          <t>-8,95; 10,61</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-20,55; -0,27</t>
+          <t>-8,97; 15,78</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-10,23; 13,74</t>
+          <t>-14,37; 10,03</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-8,11; 6,87</t>
+          <t>-8,31; 6,76</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-12,6; 3,38</t>
+          <t>-12,62; 3,61</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-6,34; 18,52</t>
+          <t>-8,67; 8,94</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-9,94%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-45,1%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>5,19%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>2,9%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>8,91%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>22,64%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-9,94%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-45,1%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>-12,16%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>-2,98%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-34,28; 59,63</t>
+          <t>-43,32; 56,19</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-34,57; 69,9</t>
+          <t>-73,26; 4,94</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-34,59; 156,69</t>
+          <t>-37,2; 76,9</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-43,97; 46,34</t>
+          <t>-31,46; 57,54</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-72,94; -0,14</t>
+          <t>-31,78; 81,16</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-39,63; 74,85</t>
+          <t>-52,07; 49,46</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-30,55; 34,28</t>
+          <t>-29,7; 33,6</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-44,6; 17,8</t>
+          <t>-46,1; 17,5</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-23,76; 95,7</t>
+          <t>-32,24; 44,95</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>2,05</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-0,86</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>4,34</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>0,12</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-1,83</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>6,89</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2,05</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-0,86</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,88</t>
+          <t>2,08</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>5,84</t>
+          <t>3,27</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 4,16</t>
+          <t>-2,73; 5,95</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,88; 2,27</t>
+          <t>-4,8; 2,77</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,64; 22,02</t>
+          <t>-0,2; 8,87</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 6,53</t>
+          <t>-4,13; 4,66</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,09; 3,26</t>
+          <t>-6,37; 2,39</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,61; 9,8</t>
+          <t>-2,67; 6,54</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 4,01</t>
+          <t>-2,03; 3,96</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 1,87</t>
+          <t>-4,29; 1,33</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,21; 13,24</t>
+          <t>-0,02; 6,67</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>11,18%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-4,68%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>23,59%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>0,6%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-9,42%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>35,53%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>11,18%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-4,68%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>17,35%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-19,88; 23,88</t>
+          <t>-13,01; 35,91</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-26,69; 13,33</t>
+          <t>-24,27; 16,87</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,16; 122,39</t>
+          <t>-0,72; 54,17</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-9,44; 39,38</t>
+          <t>-19,09; 27,69</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-25,31; 20,64</t>
+          <t>-29,44; 14,55</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,95; 58,72</t>
+          <t>-12,14; 38,29</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-8,33; 22,58</t>
+          <t>-9,36; 22,51</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-20,13; 10,71</t>
+          <t>-20,36; 7,59</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>10,44; 73,13</t>
+          <t>0,14; 39,18</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,8</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-6,9</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>3,3</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>8,87</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>3,72</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>14,89</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,8</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-6,9</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,07</t>
+          <t>14,07</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>9,08</t>
+          <t>8,87</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,61; 15,72</t>
+          <t>-6,22; 8,54</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 10,09</t>
+          <t>-13,86; -0,22</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,79; 22,24</t>
+          <t>-4,25; 11,89</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,73; 8,04</t>
+          <t>2,31; 15,98</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-13,54; -0,16</t>
+          <t>-2,14; 10,04</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,75; 10,76</t>
+          <t>6,4; 21,3</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 9,87</t>
+          <t>0,03; 10,15</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-6,15; 3,07</t>
+          <t>-5,9; 3,39</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,62; 14,33</t>
+          <t>4,1; 14,54</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>3,57%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-30,95%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>14,81%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>68,45%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>28,68%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>114,93%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>3,57%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-30,95%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>108,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>52,15%</t>
+          <t>50,95%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>16,63; 161,66</t>
+          <t>-24,89; 47,37</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-14,33; 102,46</t>
+          <t>-53,07; -2,47</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>48,77; 215,34</t>
+          <t>-17,28; 64,38</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-26,32; 44,24</t>
+          <t>11,71; 158,62</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-53,51; -0,88</t>
+          <t>-13,91; 100,65</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-17,89; 57,67</t>
+          <t>35,71; 209,36</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 65,73</t>
+          <t>0,06; 65,52</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-30,87; 19,94</t>
+          <t>-30,3; 23,35</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>17,75; 96,07</t>
+          <t>20,78; 100,14</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>1,27</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-3,28</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>3,72</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>2,36</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-0,3</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>8,51</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1,27</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-3,28</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,1</t>
+          <t>4,39</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>6,18</t>
+          <t>4,06</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 5,9</t>
+          <t>-2,18; 4,94</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 2,64</t>
+          <t>-6,67; -0,34</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,12; 18,36</t>
+          <t>-0,14; 7,24</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 4,62</t>
+          <t>-0,75; 6,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-6,51; 0,2</t>
+          <t>-3,84; 2,73</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,72; 8,28</t>
+          <t>1,15; 8,52</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 4,21</t>
+          <t>-0,7; 4,09</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 0,71</t>
+          <t>-4,32; 0,56</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,18; 10,76</t>
+          <t>1,21; 6,57</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>6,41%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-16,55%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>18,78%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>12,84%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-1,65%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>46,25%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>6,41%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-16,55%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>32,29%</t>
+          <t>21,2%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-6,72; 34,41</t>
+          <t>-10,34; 27,12</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-19,63; 15,96</t>
+          <t>-31,11; -1,78</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>15,08; 101,97</t>
+          <t>-0,49; 39,94</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-10,21; 25,26</t>
+          <t>-3,71; 35,93</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-30,17; 1,54</t>
+          <t>-19,16; 16,14</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,21; 46,1</t>
+          <t>6,0; 51,11</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 23,94</t>
+          <t>-3,33; 22,65</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-20,01; 3,96</t>
+          <t>-21,61; 2,97</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>15,24; 58,33</t>
+          <t>5,91; 36,42</t>
         </is>
       </c>
     </row>
